--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,12 +773,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Radhika</t>
+          <t>Akhila Kovuri</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rubika.ae@qualesce.com</t>
+          <t>akhila.k@qualesce.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -800,12 +800,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Akhila Kovuri</t>
+          <t>Sharanbasappa Malipatil</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>akhila.k@qualesce.com</t>
+          <t>sharanbasappa.m@qualesce.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sharanbasappa Malipatil</t>
+          <t>Nandukant Bhaskar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sharanbasappa.m@qualesce.com</t>
+          <t>nandukant.b@qualesce.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nandukant Bhaskar</t>
+          <t>Narendra C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nandukant.b@qualesce.com</t>
+          <t>narendra.c@qualesce.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Narendra C</t>
+          <t>Vikas Baburao Sajjan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>narendra.c@qualesce.com</t>
+          <t>vikasbaburao.sajjan@qualesce.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -908,12 +908,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vikas Baburao Sajjan</t>
+          <t>Shravani S</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vikasbaburao.sajjan@qualesce.com</t>
+          <t>shravani.s@qualesce.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -935,12 +935,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shravani S</t>
+          <t>Shiva shankar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shravani.s@qualesce.com</t>
+          <t>shiva.shankarb@qualesce.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -962,12 +962,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shiva shankar</t>
+          <t>Nischal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shiva.shankarb@qualesce.com</t>
+          <t>nischal.n@qualesce.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -989,12 +989,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nischal</t>
+          <t>Harshith</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nischal.n@qualesce.com</t>
+          <t>harshith.v@qualesce.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1016,12 +1016,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Harshith</t>
+          <t>Nanditha</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>harshith.v@qualesce.com</t>
+          <t>nandhitha.g@qualesce.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1035,33 +1035,6 @@
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Nanditha</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nandhitha.g@qualesce.com</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>User@123</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
